--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,17 +440,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.380000000000001" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6.25" customWidth="1" min="3" max="3"/>
-    <col width="32.38" customWidth="1" min="5" max="5"/>
-    <col width="7.25" customWidth="1" min="6" max="6"/>
-    <col width="6.63" customWidth="1" min="7" max="7"/>
-    <col width="16.75" customWidth="1" min="8" max="8"/>
-    <col width="24.75" customWidth="1" min="9" max="9"/>
+    <col width="32.38" customWidth="1" min="6" max="6"/>
+    <col width="7.25" customWidth="1" min="7" max="7"/>
+    <col width="6.63" customWidth="1" min="8" max="8"/>
+    <col width="16.75" customWidth="1" min="9" max="9"/>
+    <col width="24.75" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 무기 하나. Item.xlsx 안의 시트(Weapon·Armor·Consumable). ItemType은 enum 값 Weapon 고정(시트 이름과 같음). Acquire enum: START, STORY. 상시 사용 데이터라 Active 열 없음(10/29). AttackIDs는 Attack ID를 | 로 구분, SkillID는 Skill ID.</t>
+          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 경로(저장소 기준, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = UnitStat 열 이름(HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed), value는 정수·비율 만분율. AttackIDs·SkillID·AcquireAnim은 무기만. Acquire enum: START, STORY. 상시 사용이라 Active 없음. 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -473,6 +471,7 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -482,7 +481,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>무기별 공격 목록·스킬·획득 방식.</t>
+          <t>아이템 종류·스탯 JSON·무기 공격 목록·스킬·획득 방식.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -492,6 +491,7 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Player.StartWeapon과 무기 획득 처리가 읽는다.</t>
+          <t>Player.StartWeapon, Skill.WeaponID, 아이템 획득·장비 처리가 읽는다. 스탯은 StatJson 파일을 읽어 더함.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -511,6 +511,7 @@
       <c r="G3" s="1" t="n"/>
       <c r="H3" s="1" t="n"/>
       <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -520,7 +521,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>무기를 행 추가로 늘리기 위해(완성판 3종). 무기 획득 = 스킬 해금(10/28).</t>
+          <t>아이템을 행 추가로 늘리고, 아이템마다 다른 스탯 조합을 JSON으로 자유롭게 담기 위해. 무기 획득 = 스킬 해금(10/28).</t>
         </is>
       </c>
       <c r="C4" s="1" t="n"/>
@@ -530,6 +531,7 @@
       <c r="G4" s="1" t="n"/>
       <c r="H4" s="1" t="n"/>
       <c r="I4" s="1" t="n"/>
+      <c r="J4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -549,6 +551,7 @@
       <c r="G5" s="1" t="n"/>
       <c r="H5" s="1" t="n"/>
       <c r="I5" s="1" t="n"/>
+      <c r="J5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -573,30 +576,35 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>StatJson</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>InGstar</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>AttackIDs</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>SkillID</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Acquire</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>AcquireAnim</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -621,30 +629,35 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
+          <t>stats/item/6001.json</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>5001|5002|5003|5004</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>7001</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>START</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>ANIM_ACQ_6001</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>시작 무기. 결박 가르기는 장부방 해금(예외, 10/28)</t>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>시작 무기. 기본 스탯은 UnitStat이라 추가 스탯 없음(빈 배열)</t>
         </is>
       </c>
     </row>
@@ -667,22 +680,27 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t>stats/item/6002.json</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>STORY</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>ANIM_ACQ_6002</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>완성판, 획득 시 스킬 해금</t>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>완성판. 스탯 예시: ATK+2, 치명타 확률+2%</t>
         </is>
       </c>
     </row>
@@ -705,373 +723,99 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>stats/item/6003.json</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>STORY</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>ANIM_ACQ_6003</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>완성판, 획득 시 스킬 해금</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>[초안 10/29 · 열 구조만, 완성판 범위] 한 행 = 방어구 하나. Item.xlsx 안의 시트. ItemType enum 값 Armor 고정. ArmorSlot enum(예시, 미확정): HEAD, BODY, ACCESSORY. Acquire enum: START, STORY. 상시 사용 데이터라 Active 열 없음. 비율은 만분율.</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>방어구별 방어·회피 보정과 획득 방식.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>장비·인벤토리 처리가 읽는다. 지스타 범위 밖(인벤토리는 완성판).</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>의도</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>방어구를 행 추가로 늘리고, 개발이 시트 이름·분류를 enum으로 관리하기 위해.</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Name, Note</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>TextID</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>ArmorSlot</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Dodge</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>[초안 10/29 · 열 구조만, 완성판 범위] 한 행 = 소모품 하나. Item.xlsx 안의 시트. ItemType enum 값 Consumable 고정. ConsumableType enum(예시, 미확정): HEAL, CURE, BUFF. CureStatusID는 없애는 상태이상(PlayerState ID, 없으면 0). Acquire enum: START, STORY. 상시 사용 데이터라 Active 열 없음. 시간 ms.</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>소모품별 효과·사용 시간·최대 소지 개수.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>소모품 사용·인벤토리 처리가 읽는다. 지스타 범위 밖(회복 소모품은 완성판, 지스타 약초는 Player 탭 값).</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>의도</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>소모품을 행 추가로 늘리고, 개발이 시트 이름·분류를 enum으로 관리하기 위해.</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Name, Note</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>TextID</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>ConsumableType</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>UseTime</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>MaxStack</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>CureStatusID</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>버선</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>stats/item/6101.json</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>약초</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>stats/item/6201.json</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>예시 행. 스탯 예시: HP+40(Player.HerbHeal과 같은 값). 지스타 약초는 Player 탭 값을 씀</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>아이템 종류·스탯 JSON·무기 공격 목록·스킬·획득 방식.</t>
+          <t>JSON,아이템 종류·스탯 JSON·무기 공격 목록·스킬·획득 방식.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 경로(저장소 기준, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = UnitStat 열 이름(HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed), value는 정수·비율 만분율. AttackIDs·SkillID·AcquireAnim은 무기만. Acquire enum: START, STORY. 상시 사용이라 Active 없음. 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정).</t>
+          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 경로(저장소 기준, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = UnitStat 열 이름(HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed), value는 정수·비율 만분율. AttackIDs·SkillID·AcquireAnim은 무기만. Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -612,15 +612,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>발골칼</t>
+          <t>버선칼</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>30007</v>
+        <v>30008</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>stats/item/6001.json</t>
+          <t>stats/item/6002.json</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -652,26 +652,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>ANIM_ACQ_6001</t>
+          <t>ANIM_ACQ_6002</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>시작 무기. 기본 스탯은 UnitStat이라 추가 스탯 없음(빈 배열)</t>
+          <t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>버선칼</t>
+          <t>쇠메</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>30008</v>
+        <v>30009</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>stats/item/6002.json</t>
+          <t>stats/item/6003.json</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -695,35 +695,33 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>ANIM_ACQ_6002</t>
+          <t>ANIM_ACQ_6003</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>완성판. 스탯 예시: ATK+2, 치명타 확률+2%</t>
+          <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>6003</v>
+        <v>6101</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>쇠메</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>30009</v>
-      </c>
+          <t>버선</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>stats/item/6003.json</t>
+          <t>stats/item/6101.json</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -736,34 +734,30 @@
           <t>STORY</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>ANIM_ACQ_6003</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
+          <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>6101</v>
+        <v>6201</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>버선</t>
+          <t>약초</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Consumable</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>stats/item/6101.json</t>
+          <t>stats/item/6201.json</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -778,44 +772,18 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
+          <t>예시 행. 스탯 예시: HP+40(Player.HerbHeal과 같은 값). 지스타 약초는 Player 탭 값을 씀</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>6201</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>약초</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>stats/item/6201.json</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>STORY</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>예시 행. 스탯 예시: HP+40(Player.HerbHeal과 같은 값). 지스타 약초는 Player 탭 값을 씀</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -440,16 +440,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.380000000000001" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6.25" customWidth="1" min="3" max="3"/>
     <col width="32.38" customWidth="1" min="6" max="6"/>
-    <col width="7.25" customWidth="1" min="7" max="7"/>
-    <col width="6.63" customWidth="1" min="8" max="8"/>
-    <col width="16.75" customWidth="1" min="9" max="9"/>
+    <col width="6.63" customWidth="1" min="7" max="7"/>
+    <col width="16.75" customWidth="1" min="8" max="8"/>
+    <col width="24.75" customWidth="1" min="9" max="9"/>
     <col width="24.75" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 경로(저장소 기준, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = UnitStat 열 이름(HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed), value는 정수·비율 만분율. AttackIDs·SkillID·AcquireAnim은 무기만. Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정).</t>
+          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 경로(저장소 기준, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed), value는 정수·비율 만분율. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>JSON,아이템 종류·스탯 JSON·무기 공격 목록·스킬·획득 방식.</t>
+          <t>JSON,아이템 종류·스탯 JSON·스킬·획득 방식.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -586,25 +586,20 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>AttackIDs</t>
+          <t>SkillID</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SkillID</t>
+          <t>Acquire</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Acquire</t>
+          <t>AcquireAnim</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>AcquireAnim</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -637,25 +632,20 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>5001|5002|5003|5004</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>7001</v>
       </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>START</t>
+          <t>ANIM_ACQ_6002</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>ANIM_ACQ_6002</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</t>
         </is>
@@ -688,17 +678,17 @@
           <t>N</t>
         </is>
       </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>ANIM_ACQ_6003</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>ANIM_ACQ_6003</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
         </is>
@@ -729,13 +719,13 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>STORY</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
         </is>
@@ -765,12 +755,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>STORY</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>예시 행. 스탯 예시: HP+40(Player.HerbHeal과 같은 값). 지스타 약초는 Player 탭 값을 씀</t>
         </is>
@@ -783,7 +773,6 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -440,16 +440,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.380000000000001" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6.25" customWidth="1" min="3" max="3"/>
     <col width="32.38" customWidth="1" min="6" max="6"/>
-    <col width="6.63" customWidth="1" min="7" max="7"/>
-    <col width="16.75" customWidth="1" min="8" max="8"/>
-    <col width="24.75" customWidth="1" min="9" max="9"/>
+    <col width="7.25" customWidth="1" min="7" max="7"/>
+    <col width="6.63" customWidth="1" min="8" max="8"/>
+    <col width="16.75" customWidth="1" min="9" max="9"/>
     <col width="24.75" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 이름(저장소 stats/item/ 안, 예: 6002.json, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed), value는 정수·비율 만분율. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정).</t>
+          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 이름(저장소 stats/item/ 안, 예: 6002.json, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed, ArmorPen), value는 정수·비율 만분율. 아이템 ATK·ArmorPen은 Formula 탭 데미지 공식에 더해짐. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정). 소모품 효과 수치는 Buff 탭.</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -604,6 +604,7 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -650,6 +651,7 @@
           <t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</t>
         </is>
       </c>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -693,6 +695,7 @@
           <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
         </is>
       </c>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -730,6 +733,7 @@
           <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
         </is>
       </c>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -760,11 +764,13 @@
           <t>STORY</t>
         </is>
       </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>예시 행. 스탯 예시: HP+40(Player.HerbHeal과 같은 값). 지스타 약초는 Player 탭 값을 씀</t>
-        </is>
-      </c>
+          <t>예시 행. 스탯 예시: HP+40. 실제 회복 수치·사용 횟수는 Buff 14001(10/29)</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -773,6 +779,7 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -435,353 +435,361 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8.380000000000001" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="6.25" customWidth="1" min="3" max="3"/>
-    <col width="32.38" customWidth="1" min="6" max="6"/>
-    <col width="7.25" customWidth="1" min="7" max="7"/>
-    <col width="6.63" customWidth="1" min="8" max="8"/>
-    <col width="16.75" customWidth="1" min="9" max="9"/>
-    <col width="24.75" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 이름(저장소 stats/item/ 안, 예: 6002.json, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed, ArmorPen), value는 정수·비율 만분율. 아이템 ATK·ArmorPen은 Formula 탭 데미지 공식에 더해짐. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정). 소모품 효과 수치는 Buff 탭.</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>JSON,아이템 종류·스탯 JSON·스킬·획득 방식.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Player.StartWeapon, Skill.WeaponID, 아이템 획득·장비 처리가 읽는다. 스탯은 StatJson 파일을 읽어 더함.</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-      <c r="J3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>의도</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>아이템을 행 추가로 늘리고, 아이템마다 다른 스탯 조합을 JSON으로 자유롭게 담기 위해. 무기 획득 = 스킬 해금(10/28).</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Name, Note</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>TextID</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>StatJson</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>InGstar</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>SkillID</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Acquire</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>AcquireAnim</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6002</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>버선칼</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>30008</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>6002.json</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>7001</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>ANIM_ACQ_6002</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>6003</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>쇠메</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>30009</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>6003.json</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>STORY</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>ANIM_ACQ_6003</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6101</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>버선</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>6101.json</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>STORY</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>6201</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>약초</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>6201.json</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>STORY</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>예시 행. 스탯 예시: HP+40. 실제 회복 수치·사용 횟수는 Buff 14001(10/29)</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:K11"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col width="8.380000000000001" customWidth="1" min="1" max="1"/>
+    <ns0:col width="8" customWidth="1" min="2" max="2"/>
+    <ns0:col width="6.25" customWidth="1" min="3" max="3"/>
+    <ns0:col width="32.38" customWidth="1" min="6" max="6"/>
+    <ns0:col width="7.25" customWidth="1" min="7" max="7"/>
+    <ns0:col width="6.63" customWidth="1" min="8" max="8"/>
+    <ns0:col width="16.75" customWidth="1" min="9" max="9"/>
+    <ns0:col width="24.75" customWidth="1" min="10" max="10"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>규칙</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 이름(저장소 stats/item/ 안, 예: 6002.json, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed, ArmorPen), value는 정수·비율 만분율. 아이템 ATK·ArmorPen은 Formula 탭 데미지 공식에 더해짐. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정). 소모품 효과 수치는 Buff 탭.
+[추출 지정 규칙]
+@column Name=TextID;Type=Integer;Optional=Y;Minimum=1;ReferenceTable=Language
+@column Name=ItemType;Type=Text;AllowedValues=Weapon|Armor|Consumable
+@column Name=StatJson;Type=Text;Optional=Y
+@column Name=InGstar;Type=Flag
+@column Name=SkillID;Type=Integer;Optional=Y;Minimum=1;ReferenceTable=Skill
+@column Name=Acquire;Type=Text;AllowedValues=START|STORY
+@column Name=AcquireAnim;Type=Text;Optional=Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="n"/>
+      <ns0:c r="D1" s="1" t="n"/>
+      <ns0:c r="E1" s="1" t="n"/>
+      <ns0:c r="F1" s="1" t="n"/>
+      <ns0:c r="G1" s="1" t="n"/>
+      <ns0:c r="H1" s="1" t="n"/>
+      <ns0:c r="I1" s="1" t="n"/>
+      <ns0:c r="J1" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기능</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>JSON,아이템 종류·스탯 JSON·스킬·획득 방식.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="n"/>
+      <ns0:c r="D2" s="1" t="n"/>
+      <ns0:c r="E2" s="1" t="n"/>
+      <ns0:c r="F2" s="1" t="n"/>
+      <ns0:c r="G2" s="1" t="n"/>
+      <ns0:c r="H2" s="1" t="n"/>
+      <ns0:c r="I2" s="1" t="n"/>
+      <ns0:c r="J2" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>역할</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Player.StartWeapon, Skill.WeaponID, 아이템 획득·장비 처리가 읽는다. 스탯은 StatJson 파일을 읽어 더함.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" s="1" t="n"/>
+      <ns0:c r="D3" s="1" t="n"/>
+      <ns0:c r="E3" s="1" t="n"/>
+      <ns0:c r="F3" s="1" t="n"/>
+      <ns0:c r="G3" s="1" t="n"/>
+      <ns0:c r="H3" s="1" t="n"/>
+      <ns0:c r="I3" s="1" t="n"/>
+      <ns0:c r="J3" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>의도</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>아이템을 행 추가로 늘리고, 아이템마다 다른 스탯 조합을 JSON으로 자유롭게 담기 위해. 무기 획득 = 스킬 해금(10/28).</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" s="1" t="n"/>
+      <ns0:c r="D4" s="1" t="n"/>
+      <ns0:c r="E4" s="1" t="n"/>
+      <ns0:c r="F4" s="1" t="n"/>
+      <ns0:c r="G4" s="1" t="n"/>
+      <ns0:c r="H4" s="1" t="n"/>
+      <ns0:c r="I4" s="1" t="n"/>
+      <ns0:c r="J4" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>비고</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name, Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" s="1" t="n"/>
+      <ns0:c r="D5" s="1" t="n"/>
+      <ns0:c r="E5" s="1" t="n"/>
+      <ns0:c r="F5" s="1" t="n"/>
+      <ns0:c r="G5" s="1" t="n"/>
+      <ns0:c r="H5" s="1" t="n"/>
+      <ns0:c r="I5" s="1" t="n"/>
+      <ns0:c r="J5" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TextID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ItemType</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>StatJson</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>InGstar</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SkillID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Acquire</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AcquireAnim</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K6" s="2" t="n"/>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="3" t="n">
+        <ns0:v>6002</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>버선칼</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" s="3" t="n">
+        <ns0:v>30008</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Weapon</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>6002.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G7" s="3" t="n">
+        <ns0:v>7001</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>START</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ANIM_ACQ_6002</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K7" s="3" t="n"/>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" s="3" t="n">
+        <ns0:v>6003</ns0:v>
+      </ns0:c>
+      <ns0:c r="B8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>쇠메</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" s="3" t="n">
+        <ns0:v>30009</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Weapon</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>6003.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>N</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>STORY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ANIM_ACQ_6003</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>완성판. 스탯 예시: ATK+6, 이동 속도-50</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K8" s="3" t="n"/>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" s="3" t="n">
+        <ns0:v>6101</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>버선</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C9" s="3" t="n"/>
+      <ns0:c r="D9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Armor</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>6101.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>N</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>STORY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I9" s="3" t="n"/>
+      <ns0:c r="J9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K9" s="3" t="n"/>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="3" t="n">
+        <ns0:v>6201</ns0:v>
+      </ns0:c>
+      <ns0:c r="B10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>약초</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumable</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>6201.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>N</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>STORY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I10" s="3" t="n"/>
+      <ns0:c r="J10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>예시 행. 스탯 예시: HP+40. 실제 회복 수치·사용 횟수는 Buff 14001(10/29)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K10" s="3" t="n"/>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" s="3" t="n"/>
+      <ns0:c r="B11" s="3" t="n"/>
+      <ns0:c r="D11" s="3" t="n"/>
+      <ns0:c r="E11" s="3" t="n"/>
+      <ns0:c r="F11" s="3" t="n"/>
+      <ns0:c r="I11" s="3" t="n"/>
+      <ns0:c r="K11" s="3" t="n"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</ns0:worksheet>
 </file>
--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -435,33 +435,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:K11"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="8.380000000000001" customWidth="1" min="1" max="1"/>
-    <ns0:col width="8" customWidth="1" min="2" max="2"/>
-    <ns0:col width="6.25" customWidth="1" min="3" max="3"/>
-    <ns0:col width="32.38" customWidth="1" min="6" max="6"/>
-    <ns0:col width="7.25" customWidth="1" min="7" max="7"/>
-    <ns0:col width="6.63" customWidth="1" min="8" max="8"/>
-    <ns0:col width="16.75" customWidth="1" min="9" max="9"/>
-    <ns0:col width="24.75" customWidth="1" min="10" max="10"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>규칙</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 이름(저장소 stats/item/ 안, 예: 6002.json, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritMult, Poise, MoveSpeed, ArmorPen), value는 정수·비율 만분율. 아이템 ATK·ArmorPen은 Formula 탭 데미지 공식에 더해짐. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정). 소모품 효과 수치는 Buff 탭.
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8.380000000000001" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6.25" customWidth="1" min="3" max="3"/>
+    <col width="32.38" customWidth="1" min="6" max="6"/>
+    <col width="7.25" customWidth="1" min="7" max="7"/>
+    <col width="6.63" customWidth="1" min="8" max="8"/>
+    <col width="16.75" customWidth="1" min="9" max="9"/>
+    <col width="24.75" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>한 행 = 아이템 하나(무기·방어구·소모품을 한 시트에). ItemType enum: Weapon, Armor, Consumable. StatJson = 그 아이템 스탯 JSON 파일 이름(저장소 stats/item/ 안, 예: 6002.json, 없으면 빈칸). JSON은 [{"statType":"ATK","value":2}] 배열, statType enum = 플레이어 스탯 열 이름과 똑같이(UnitStat의 HP, ATK, DEF, Dodge, Crit, CritDamage, Poise, MoveSpeed, ArmorPen), value는 정수·비율 만분율. 아이템 ATK·ArmorPen은 Formula 탭 데미지 공식에 더해짐. SkillID·AcquireAnim은 무기만. 무기 평타(타수·배율·타이밍)는 데이터로 두지 않고 개발에서 처리, 무기 차이는 StatJson 스탯으로만 줌(10/29). Acquire enum: START, STORY. 상시 사용이라 Active 없음. 무기는 버선칼(시작)·쇠메 2종. 발골칼은 해체 연출용이라 아이템이 아님(6001 비움, 번호 재사용 안 함, 10/29). 방어구·소모품 행과 모든 스탯 값은 예시(10/29, 미확정). 소모품 효과 수치는 Buff 탭.
 [추출 지정 규칙]
 @column Name=TextID;Type=Integer;Optional=Y;Minimum=1;ReferenceTable=Language
 @column Name=ItemType;Type=Text;AllowedValues=Weapon|Armor|Consumable
@@ -469,327 +469,327 @@
 @column Name=InGstar;Type=Flag
 @column Name=SkillID;Type=Integer;Optional=Y;Minimum=1;ReferenceTable=Skill
 @column Name=Acquire;Type=Text;AllowedValues=START|STORY
-@column Name=AcquireAnim;Type=Text;Optional=Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" s="1" t="n"/>
-      <ns0:c r="D1" s="1" t="n"/>
-      <ns0:c r="E1" s="1" t="n"/>
-      <ns0:c r="F1" s="1" t="n"/>
-      <ns0:c r="G1" s="1" t="n"/>
-      <ns0:c r="H1" s="1" t="n"/>
-      <ns0:c r="I1" s="1" t="n"/>
-      <ns0:c r="J1" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>기능</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>JSON,아이템 종류·스탯 JSON·스킬·획득 방식.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" s="1" t="n"/>
-      <ns0:c r="D2" s="1" t="n"/>
-      <ns0:c r="E2" s="1" t="n"/>
-      <ns0:c r="F2" s="1" t="n"/>
-      <ns0:c r="G2" s="1" t="n"/>
-      <ns0:c r="H2" s="1" t="n"/>
-      <ns0:c r="I2" s="1" t="n"/>
-      <ns0:c r="J2" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>역할</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Player.StartWeapon, Skill.WeaponID, 아이템 획득·장비 처리가 읽는다. 스탯은 StatJson 파일을 읽어 더함.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C3" s="1" t="n"/>
-      <ns0:c r="D3" s="1" t="n"/>
-      <ns0:c r="E3" s="1" t="n"/>
-      <ns0:c r="F3" s="1" t="n"/>
-      <ns0:c r="G3" s="1" t="n"/>
-      <ns0:c r="H3" s="1" t="n"/>
-      <ns0:c r="I3" s="1" t="n"/>
-      <ns0:c r="J3" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>의도</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>아이템을 행 추가로 늘리고, 아이템마다 다른 스탯 조합을 JSON으로 자유롭게 담기 위해. 무기 획득 = 스킬 해금(10/28).</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="1" t="n"/>
-      <ns0:c r="D4" s="1" t="n"/>
-      <ns0:c r="E4" s="1" t="n"/>
-      <ns0:c r="F4" s="1" t="n"/>
-      <ns0:c r="G4" s="1" t="n"/>
-      <ns0:c r="H4" s="1" t="n"/>
-      <ns0:c r="I4" s="1" t="n"/>
-      <ns0:c r="J4" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>비고</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name, Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C5" s="1" t="n"/>
-      <ns0:c r="D5" s="1" t="n"/>
-      <ns0:c r="E5" s="1" t="n"/>
-      <ns0:c r="F5" s="1" t="n"/>
-      <ns0:c r="G5" s="1" t="n"/>
-      <ns0:c r="H5" s="1" t="n"/>
-      <ns0:c r="I5" s="1" t="n"/>
-      <ns0:c r="J5" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>TextID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ItemType</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>StatJson</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>InGstar</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>SkillID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Acquire</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>AcquireAnim</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K6" s="2" t="n"/>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="3" t="n">
-        <ns0:v>6002</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>버선칼</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C7" s="3" t="n">
-        <ns0:v>30008</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Weapon</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>6002.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G7" s="3" t="n">
-        <ns0:v>7001</ns0:v>
-      </ns0:c>
-      <ns0:c r="H7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>START</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ANIM_ACQ_6002</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K7" s="3" t="n"/>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="3" t="n">
-        <ns0:v>6003</ns0:v>
-      </ns0:c>
-      <ns0:c r="B8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>쇠메</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C8" s="3" t="n">
-        <ns0:v>30009</ns0:v>
-      </ns0:c>
-      <ns0:c r="D8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Weapon</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>6003.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>N</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>STORY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ANIM_ACQ_6003</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>완성판. 스탯 예시: ATK+6, 이동 속도-50</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K8" s="3" t="n"/>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="3" t="n">
-        <ns0:v>6101</ns0:v>
-      </ns0:c>
-      <ns0:c r="B9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>버선</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C9" s="3" t="n"/>
-      <ns0:c r="D9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Armor</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>6101.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>N</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>STORY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I9" s="3" t="n"/>
-      <ns0:c r="J9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K9" s="3" t="n"/>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="3" t="n">
-        <ns0:v>6201</ns0:v>
-      </ns0:c>
-      <ns0:c r="B10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>약초</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Consumable</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>6201.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>N</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>STORY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I10" s="3" t="n"/>
-      <ns0:c r="J10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>예시 행. 스탯 예시: HP+40. 실제 회복 수치·사용 횟수는 Buff 14001(10/29)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K10" s="3" t="n"/>
-    </ns0:row>
-    <ns0:row r="11">
-      <ns0:c r="A11" s="3" t="n"/>
-      <ns0:c r="B11" s="3" t="n"/>
-      <ns0:c r="D11" s="3" t="n"/>
-      <ns0:c r="E11" s="3" t="n"/>
-      <ns0:c r="F11" s="3" t="n"/>
-      <ns0:c r="I11" s="3" t="n"/>
-      <ns0:c r="K11" s="3" t="n"/>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</ns0:worksheet>
+@column Name=AcquireAnim;Type=Text;Optional=Y</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>JSON,아이템 종류·스탯 JSON·스킬·획득 방식.</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Player.StartWeapon, Skill.WeaponID, 아이템 획득·장비 처리가 읽는다. 스탯은 StatJson 파일을 읽어 더함.</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>의도</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>아이템을 행 추가로 늘리고, 아이템마다 다른 스탯 조합을 JSON으로 자유롭게 담기 위해. 무기 획득 = 스킬 해금(10/28).</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
+      <c r="I4" s="1" t="n"/>
+      <c r="J4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Name, Note</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+      <c r="I5" s="1" t="n"/>
+      <c r="J5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>TextID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>StatJson</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>InGstar</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>SkillID</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Acquire</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>AcquireAnim</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6002</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>버선칼</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>30008</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>6002.json</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>7001</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>ANIM_ACQ_6002</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6003</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>쇠메</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>30009</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>6003.json</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>ANIM_ACQ_6003</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6101</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>버선</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>6101.json</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>예시 행. 스탯 예시: 회피+2%, 이동 속도+50</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>약초</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>6201.json</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>예시 행. 스탯 예시: HP+40. 실제 회복 수치·사용 횟수는 Buff 14001(10/29)</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>시작 무기(10/29 김현호). 스탯 예시: ATK+2, 치명타 확률+2%</t>
+          <t>시작 무기(10/29 김현호). 지스타 무기는 이것 1종(10/30). 스탯 예시: ATK+2, 치명타 확률+2%</t>
         </is>
       </c>
       <c r="K7" s="3" t="n"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
+          <t>보류(10/30 회의, 지스타 무기 1종). 완성판. 스탯 예시: ATK+6, 이동 속도-50</t>
         </is>
       </c>
       <c r="K8" s="3" t="n"/>
@@ -775,7 +775,7 @@
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>예시 행. 스탯 예시: HP+40. 실제 회복 수치·사용 횟수는 Buff 14001(10/29)</t>
+          <t>예시 행. 지스타는 아이템 시스템 미사용(10/30): 약초는 이 행이 아니라 Buff 14001 값(즉시 회복 HP+40, 3회)만 씁니다</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>시작 무기(10/29 김현호). 지스타 무기는 이것 1종(10/30). 스탯 예시: ATK+2, 치명타 확률+2%</t>
+          <t>시작 무기(10/29 김현호). 지스타 무기는 이것 1종(10/30). 스탯 예시: ATK+2, 치명타 확률+2%. 지스타 아이템 시스템 미사용 시 이 스탯 적용 여부는 확인 중</t>
         </is>
       </c>
       <c r="K7" s="3" t="n"/>

--- a/tables/Item.xlsx
+++ b/tables/Item.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>시작 무기(10/29 김현호). 지스타 무기는 이것 1종(10/30). 스탯 예시: ATK+2, 치명타 확률+2%. 지스타 아이템 시스템 미사용 시 이 스탯 적용 여부는 확인 중</t>
+          <t>시작 무기(10/29 김현호). 지스타 무기는 이것 1종(10/30). 스탯 예시: ATK+2, 치명타 확률+2%. 지스타는 아이템 미사용이라 이 스탯을 UnitStat 1001(막손)에 임시로 합침, 완성판에서 분리(10/30)</t>
         </is>
       </c>
       <c r="K7" s="3" t="n"/>
